--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/18_Darlehenskonto_und_Saldo.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/18_Darlehenskonto_und_Saldo.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kapitalbewegungen" sheetId="1" r:id="R39e3f62811a84f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zinsen_Gebuehren" sheetId="2" r:id="R6380e0941aa74da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gebuehr_Valuta" sheetId="3" r:id="Rc7749a68b0c8482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo_15_09_2026" sheetId="4" r:id="Rf848c91797b245c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kapitalbewegungen" sheetId="1" r:id="R75bab3288e904ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zinsen_Gebuehren" sheetId="2" r:id="R2813cc23a9634274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gebuehr_Valuta" sheetId="3" r:id="Re036caa3cee140e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo_15_09_2026" sheetId="4" r:id="R8d0e72c3ebad4e31"/>
   </x:sheets>
 </x:workbook>
 </file>
